--- a/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
+++ b/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
@@ -1385,7 +1385,7 @@
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DEC-0186</t>
+          <t>DEC-0177</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DEC-0187</t>
+          <t>DEC-0178</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>DEC-0188</t>
+          <t>DEC-0179</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DEC-0202</t>
+          <t>DEC-0193</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DEC-0206</t>
+          <t>DEC-0197</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DEC-0210</t>
+          <t>DEC-0201</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DEC-0214</t>
+          <t>DEC-0205</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1613,7 +1613,7 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three </t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three ||| FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DEC-0215</t>
+          <t>DEC-0206</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DEC-0220</t>
+          <t>DEC-0211</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DEC-0221</t>
+          <t>DEC-0212</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DEC-0227</t>
+          <t>DEC-0218</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>DEC-0238</t>
+          <t>DEC-0229</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">

--- a/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
+++ b/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
@@ -1477,7 +1477,7 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — interest and dividends</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — interest and dividends ||| the rulings ledger being retired (moneykeel_rulings.json · G47) — originally: the design Changelog, 2026-08-28 (approved by JJ), quoted from its Why column — swept into this ledger 2026-09-28</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1613,7 +1613,7 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three ||| FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three</t>
+          <t xml:space="preserve">FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1647,7 +1647,7 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Standard — an `audit` folder and type</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Standard — an `audit` folder and type ||| the rulings ledger being retired (moneykeel_rulings.json · G40) — originally: the design Changelog, 2026-09-01 (approved by JJ) — swept into this ledger 2026-09-28</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1681,7 +1681,7 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-02 · Plan hub · Retirement cockpit</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-02 · Plan hub · Retirement cockpit ||| the rulings ledger being retired (moneykeel_rulings.json · G44) — originally: the design Changelog, 2026-09-02 (approved by JJ) — swept into this ledger 2026-09-28</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">

--- a/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
+++ b/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Wording asks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wording asks'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wording asks'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -583,31 +583,29 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>DEC-0004</t>
+          <t>DEC-0008</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Cash flow</t>
+          <t>All screens</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The Spending tab shows the month’s total at the top, then each recent expense with a small label saying where it came from — entered by hand, or imported. Two decisions:
-1. A card compares each category against what you planned to spend on it.
-2. On day one the tab shows three doors to get started rather than an empty screen.</t>
+          <t>Two type sizes, decided: a dense table — the winners and laggards list, the holdings list — keeps its smaller approved size, because a table of twenty rows at hero size is unreadable. The 17-point minimum for money applies to the big headline figures and to money standing on its own.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-19 · Cash flow ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-19 · Cash flow</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · All screens ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · All screens</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -619,7 +617,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DEC-0008</t>
+          <t>DEC-0009</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -629,19 +627,19 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>All screens</t>
+          <t>Screen inventory</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Two type sizes, decided: a dense table — the winners and laggards list, the holdings list — keeps its smaller approved size, because a table of twenty rows at hero size is unreadable. The 17-point minimum for money applies to the big headline figures and to money standing on its own.</t>
+          <t>Estate, Insurance, Tax organizer, Job safety and Credit STAY in the first launch. They are not cut: each remains a row on the launch sign-off list and each has to pass it.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · All screens ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · All screens</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · Screen inventory ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · Screen inventory</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -653,7 +651,7 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DEC-0009</t>
+          <t>DEC-0010</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -663,19 +661,21 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Screen inventory</t>
+          <t>All screens</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Estate, Insurance, Tax organizer, Job safety and Credit STAY in the first launch. They are not cut: each remains a row on the launch sign-off list and each has to pass it.</t>
+          <t>Every chart in the app moves to one colour set, checked to be readable by people who are colourblind — so Cash is the same colour everywhere it appears. Two decisions:
+1. Every affected chart is redrawn in the new colours as a picture first.
+2. Nothing changes in the app until those pictures are approved.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · Screen inventory ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · Screen inventory</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · All screens ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · All screens</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DEC-0010</t>
+          <t>DEC-0011</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -697,21 +697,19 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>All screens</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Every chart in the app moves to one colour set, checked to be readable by people who are colourblind — so Cash is the same colour everywhere it appears. Two decisions:
-1. Every affected chart is redrawn in the new colours as a picture first.
-2. Nothing changes in the app until those pictures are approved.</t>
+          <t>A STANDING RULE: every approval he gives gets a dated row in the design Changelog the same day, beside the mock it approves. An approval that lives only in a conversation is lost.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · All screens ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · All screens</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · Process ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · Process</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -723,54 +721,20 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DEC-0011</t>
+          <t>DEC-0019</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Connected accounts (ingest)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>A STANDING RULE: every approval he gives gets a dated row in the design Changelog the same day, beside the mock it approves. An approval that lives only in a conversation is lost.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-28 · Process ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-28 · Process</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0019</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Connected accounts (ingest)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>When you link a brokerage, the app takes the account's total straight from the broker. Vanguard sent back no total at all, while the account really held $132,000 — so it showed $0. Four decisions:
 1. When the broker gives no total, or gives zero, add up EVERYTHING THE ACCOUNT HOLDS instead: every holding in it at today's price — stocks, ETFs, funds, bonds, CDs, Treasuries — plus any options, plus the uninvested cash sitting in it. Not just the shares: an account is whatever is in it.
@@ -779,11 +743,45 @@
 4. Only for accounts held in US dollars, and an account that is genuinely empty stays at zero. A foreign-currency account's holdings are priced in that currency, so adding them up would produce a dollar figure that is not real; and an empty account is empty, not unknown.</t>
         </is>
       </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-31 · Connected accounts (ingest) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-31 · Connected accounts (ingest)</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DEC-0024</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Plan hub (redesign in review)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Every row on the Plan screen is a complete question in your own voice: “When can I retire?”, “Can I afford it?”, “When should I claim Social Security?”, “Which account do I draw from first?”, “Is a Roth move worth it?”, “Can I spend more?”. He dropped the word “all” from the second one.</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-07-31 · Connected accounts (ingest) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-07-31 · Connected accounts (ingest)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-01 · Plan hub (redesign in review) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-01 · Plan hub (redesign in review)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -795,29 +793,29 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DEC-0024</t>
+          <t>DEC-0027</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Plan hub (redesign in review)</t>
+          <t>Screen inventory</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Every row on the Plan screen is a complete question in your own voice: “When can I retire?”, “Can I afford it?”, “When should I claim Social Security?”, “Which account do I draw from first?”, “Is a Roth move worth it?”, “Can I spend more?”. He dropped the word “all” from the second one.</t>
+          <t>The older screens that nothing currently links to — the income detail page, the previous income, invest and savings screens, Tips and Rewards — are KEPT rather than deleted, because they are reusable if the app is later built for a different age group. The menu is unchanged.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-01 · Plan hub (redesign in review) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-01 · Plan hub (redesign in review)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Screen inventory ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Screen inventory</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -829,7 +827,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DEC-0027</t>
+          <t>DEC-0028</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -839,19 +837,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Screen inventory</t>
+          <t>Plan / big costs</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>The older screens that nothing currently links to — the income detail page, the previous income, invest and savings screens, Tips and Rewards — are KEPT rather than deleted, because they are reusable if the app is later built for a different age group. The menu is unchanged.</t>
+          <t>The mock for entering big upcoming costs is approved. The entry screen, the effect on the projection and the row on the Plan screen all build into build 48.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Screen inventory ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Screen inventory</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Plan / big costs ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Plan / big costs</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -863,7 +861,7 @@
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>DEC-0028</t>
+          <t>DEC-0030</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -873,19 +871,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Plan / big costs</t>
+          <t>Invest / holding detail</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>The mock for entering big upcoming costs is approved. The entry screen, the effect on the projection and the row on the Plan screen all build into build 48.</t>
+          <t>The “what if I had moved this money” card stays on the holding page. It was missing from the mock, and that was a gap in the drawing rather than a decision to remove it.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Plan / big costs ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Plan / big costs</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Invest / holding detail ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Invest / holding detail</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -897,7 +895,7 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DEC-0030</t>
+          <t>DEC-0033</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -907,19 +905,19 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Invest / holding detail</t>
+          <t>Menu (TopBar)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>The “what if I had moved this money” card stays on the holding page. It was missing from the mock, and that was a gap in the drawing rather than a decision to remove it.</t>
+          <t>Rewards, Tips and Build credit come OFF the menu for the 55-to-70 audience. College planner and Estate stay. Nothing is deleted from the code — the screens remain, they are just not offered to this audience.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Invest / holding detail ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Invest / holding detail</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Menu (TopBar) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Menu (TopBar)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -931,7 +929,7 @@
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>DEC-0033</t>
+          <t>DEC-0035</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -941,19 +939,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Menu (TopBar)</t>
+          <t>SS · multi-goal · Roth</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Rewards, Tips and Build credit come OFF the menu for the 55-to-70 audience. College planner and Estate stay. Nothing is deleted from the code — the screens remain, they are just not offered to this audience.</t>
+          <t>The plus-and-minus steppers stay, rather than becoming sliders, because someone aged 65 and over needs to land on an exact figure. The design sheet is updated to match what is built.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Menu (TopBar) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Menu (TopBar)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · SS · multi-goal · Roth ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · SS · multi-goal · Roth</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -965,7 +963,7 @@
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DEC-0035</t>
+          <t>DEC-0038</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,19 +973,19 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SS · multi-goal · Roth</t>
+          <t>Connect flow (F1)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>The plus-and-minus steppers stay, rather than becoming sliders, because someone aged 65 and over needs to land on an exact figure. The design sheet is updated to match what is built.</t>
+          <t>The provider change is put ON HOLD while he evaluates Plaid, SnapTrade and Teller himself. No code and no dependency changes in the meantime — nothing is built on a choice not yet made.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · SS · multi-goal · Roth ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · SS · multi-goal · Roth</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Connect flow (F1) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Connect flow (F1)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -999,7 +997,7 @@
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>DEC-0037</t>
+          <t>DEC-0039</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1009,19 +1007,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Connect flow (F1)</t>
+          <t>Home (retroactive to 2026-07-16)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>SnapTrade is dropped as the way accounts are linked, and Plaid is taken up for the beta. The reason is privacy: he saw connected financial data displayed inside SnapTrade’s own dashboard. The migration is the next piece of work AFTER build 48, and the app is built so the provider can be swapped without the rest changing. It also unlocks importing credit-card transactions.</t>
+          <t>The floating “+Expense” button comes off the Home screen. Logging an expense lives on Cash flow only, so there is one place to do it.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Connect flow (F1) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Connect flow (F1)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Home (retroactive to 2026-07-16) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Home (retroactive to 2026-07-16)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1033,29 +1031,29 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DEC-0038</t>
+          <t>DEC-0045</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Connect flow (F1)</t>
+          <t>Alternatives capture</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>The provider change is put ON HOLD while he evaluates Plaid, SnapTrade and Teller himself. No code and no dependency changes in the meantime — nothing is built on a choice not yet made.</t>
+          <t>Private equity and hedge funds come OUT of the first phase — his instruction, keep it simple. They are removed from the options you can pick when adding an investment, but the app still understands them, so anything already saved as one still shows correctly.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Connect flow (F1) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Connect flow (F1)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Alternatives capture ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Alternatives capture</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1067,29 +1065,29 @@
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>DEC-0039</t>
+          <t>DEC-0046</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Home (retroactive to 2026-07-16)</t>
+          <t>Navigation (all surfaces)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>The floating “+Expense” button comes off the Home screen. Logging an expense lives on Cash flow only, so there is one place to do it.</t>
+          <t>The Invest tab is renamed PERFORMANCE, so the pair reads Net worth and Performance — his pick. It changes in one place and sweeps the bottom bar, the menu and the desktop sidebar together.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-02 · Home (retroactive to 2026-07-16) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-02 · Home (retroactive to 2026-07-16)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Navigation (all surfaces) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Navigation (all surfaces)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1101,7 +1099,7 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DEC-0045</t>
+          <t>DEC-0047</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1111,78 +1109,10 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Alternatives capture</t>
+          <t>Net worth</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Private equity and hedge funds come OUT of the first phase — his instruction, keep it simple. They are removed from the options you can pick when adding an investment, but the app still understands them, so anything already saved as one still shows correctly.</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Alternatives capture ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Alternatives capture</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0046</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Navigation (all surfaces)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>The Invest tab is renamed PERFORMANCE, so the pair reads Net worth and Performance — his pick. It changes in one place and sweeps the bottom bar, the menu and the desktop sidebar together.</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Navigation (all surfaces) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Navigation (all surfaces)</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0047</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Three decisions about the Net worth screen:
 1. The By type view is REMOVED, which settles the open question about it.
@@ -1190,36 +1120,36 @@
 3. Two ways of grouping remain: By category and By institution. The Investments total is the same figure as the Performance total, by definition, so the two screens cannot disagree.</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>DEC-0051</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Net worth / Performance / engines</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Cash means cash only. Three decisions:
 1. A money-market fund is classed as Stocks and funds, not cash — it pays dividends.
@@ -1227,11 +1157,79 @@
 3. This replaces the earlier rules that treated money-market funds as cash and split CDs by whether they ran twelve months. A CD’s interest is its balance times its stated rate.</t>
         </is>
       </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth / Performance / engines ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth / Performance / engines</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DEC-0052</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Three refinements to the Net worth screen: a collapsed group shows its count on a quieter second line; there is at least 16 pixels of space before a column of numbers; and every label on the doughnut is the same weight.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>DEC-0053</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>All five tabs</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>The green section bands are built on all five main screens, from ONE shared piece of screen rather than five copies — so the next change to a band changes every band. Section totals sit on the band itself, and entry screens use the lighter sub-band. The roughly 25 detail screens follow next.</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth / Performance / engines ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth / Performance / engines</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · All five tabs ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · All five tabs</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1243,7 +1241,7 @@
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>DEC-0052</t>
+          <t>DEC-0061</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1253,19 +1251,21 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Net worth (+ engine)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Three refinements to the Net worth screen: a collapsed group shows its count on a quieter second line; there is at least 16 pixels of space before a column of numbers; and every label on the doughnut is the same weight.</t>
+          <t>When something is missing from your figures, the screen says so in a line inside the page — never a pop-up. Two decisions:
+1. Five things count as a gap: a holding with no price, a connection that has stopped updating, no dividend records, a hand-entered value that is now old, and a source that shared less history than the figure covers.
+2. The banner counts and NAMES each gap, and tapping it opens a sheet that fixes them.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth</t>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth (+ engine) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth (+ engine)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1277,90 +1277,20 @@
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>DEC-0053</t>
+          <t>DEC-0069</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>All five tabs</t>
+          <t>Net worth (by institution)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>The green section bands are built on all five main screens, from ONE shared piece of screen rather than five copies — so the next change to a band changes every band. Section totals sit on the band itself, and entry screens use the lighter sub-band. The roughly 25 detail screens follow next.</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · All five tabs ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · All five tabs</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0061</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Net worth (+ engine)</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>When something is missing from your figures, the screen says so in a line inside the page — never a pop-up. Two decisions:
-1. Five things count as a gap: a holding with no price, a connection that has stopped updating, no dividend records, a hand-entered value that is now old, and a source that shared less history than the figure covers.
-2. The banner counts and NAMES each gap, and tapping it opens a sheet that fixes them.</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-04 · Net worth (+ engine) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-04 · Net worth (+ engine)</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0069</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Net worth (by institution)</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>The By institution view is rebuilt to work the same way as By category. Four decisions:
 1. Institution groups collapse and expand.
@@ -1369,11 +1299,79 @@
 4. A closed group shows how many accounts are inside it.</t>
         </is>
       </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-10 · Net worth (by institution) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-10 · Net worth (by institution)</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>DEC-0177</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Income — mock</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>The income mock is approved: 14 screens in one document, with the 13 earlier income mocks archived so there is one live file rather than a folder to choose from.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — mock</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>DEC-0178</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Income — tax band, where it belongs</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Your tax band is worked out ONCE, from your total income, and every screen reads that one figure. The base-pay screen does not work out a band of its own — a band is set by everything you are taxed on together, so a screen that sees only your wage would show the wrong one.</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-07-19.xlsx · Changelog · 2026-08-10 · Net worth (by institution) ||| FCC-core-detailed-design-v1.3-2026-08-12.xlsx · Changelog · 2026-08-10 · Net worth (by institution)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — tax band, where it belongs</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1385,7 +1383,7 @@
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>DEC-0177</t>
+          <t>DEC-0179</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1395,19 +1393,21 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Income — mock</t>
+          <t>Income — interest and dividends</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>The income mock is approved: 14 screens in one document, with the 13 earlier income mocks archived so there is one live file rather than a folder to choose from.</t>
+          <t>Interest and dividends are taxed but are not money you can spend, unless you tell us they reach your bank. Two decisions:
+1. In most accounts they are reinvested where they are earned and never arrive, so they are taken out of your spendable take-home.
+2. The tax on them still comes out, because it is real — so simply deleting them would have been wrong in the other direction.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — mock</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — interest and dividends ||| the rulings ledger being retired (moneykeel_rulings.json · G47) — originally: the design Changelog, 2026-08-28 (approved by JJ), quoted from its Why column — swept into this ledger 2026-09-28</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1416,32 +1416,32 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DEC-0178</t>
+          <t>DEC-0193</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Income — tax band, where it belongs</t>
+          <t>Standard — type list gains `master`; onboarding budget 37 → 38</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Your tax band is worked out ONCE, from your total income, and every screen reads that one figure. The base-pay screen does not work out a band of its own — a band is set by everything you are taxed on together, so a screen that sees only your wage would show the wrong one.</t>
+          <t>The file-naming standard gains `master` as a permitted type, and the onboarding question count goes from 37 to 38 for the new filing-status question.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — tax band, where it belongs</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-28 · Standard — type list gains `master`; onboarding budget 37 → 38</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1453,31 +1453,29 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>DEC-0179</t>
+          <t>DEC-0197</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Income — interest and dividends</t>
+          <t>Income — the tax rate built (mock income-v5)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Interest and dividends are taxed but are not money you can spend, unless you tell us they reach your bank. Two decisions:
-1. In most accounts they are reinvested where they are earned and never arrive, so they are taken out of your spendable take-home.
-2. The tax on them still comes out, because it is real — so simply deleting them would have been wrong in the other direction.</t>
+          <t>Where your tax rate comes from, in order: TYPED off your payslip, IMPLIED by what you said lands in your bank, or OUR estimate — and each one says whose it is on the screen. A person could tell base pay exactly what lands and every other screen still estimated it, $572 a month apart.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-27 · Income — interest and dividends ||| the rulings ledger being retired (moneykeel_rulings.json · G47) — originally: the design Changelog, 2026-08-28 (approved by JJ), quoted from its Why column — swept into this ledger 2026-09-28</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-28 · Income — the tax rate built (mock income-v5)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1486,10 +1484,10 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DEC-0193</t>
+          <t>DEC-0201</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1499,19 +1497,19 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Standard — type list gains `master`; onboarding budget 37 → 38</t>
+          <t>Cash flow — Your income, all of it (mock income-v5, 5a and 5b)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>The file-naming standard gains `master` as a permitted type, and the onboarding question count goes from 37 to 38 for the new filing-status question.</t>
+          <t>A new screen showing all your income: two totals, labelled — what lands in your bank each month, and what the year is taxed on. A fresh account keeps both headings and shows no invented $0.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-28 · Standard — type list gains `master`; onboarding budget 37 → 38</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-28 · Cash flow — Your income, all of it (mock income-v5, 5a and 5b)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1523,29 +1521,29 @@
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DEC-0197</t>
+          <t>DEC-0205</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Income — the tax rate built (mock income-v5)</t>
+          <t>Every statutory constant checked against its published source — three errors found</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Where your tax rate comes from, in order: TYPED off your payslip, IMPLIED by what you said lands in your bank, or OUR estimate — and each one says whose it is on the screen. A person could tell base pay exactly what lands and every other screen still estimated it, $572 a month apart.</t>
+          <t>Every figure set by law is typed in from the published source. The first run against the real figures found three errors: the IRA limits were a year out of date, the bigger catch-up allowance for ages 60 to 63 was missing entirely in an app built for ages 55 to 70, and four of the required-withdrawal divisors were slightly wrong from being interpolated rather than typed.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-28 · Income — the tax rate built (mock income-v5)</t>
+          <t xml:space="preserve">FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1557,29 +1555,29 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DEC-0201</t>
+          <t>DEC-0206</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Cash flow — Your income, all of it (mock income-v5, 5a and 5b)</t>
+          <t>Standard — an `audit` folder and type</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>A new screen showing all your income: two totals, labelled — what lands in your bank each month, and what the year is taxed on. A fresh account keeps both headings and shows no invented $0.</t>
+          <t>Records of checking the work get their own folder. His ruling: checking the work is its own kind of paper. Filing a device-test sheet under the standards folder hid the record of what had been verified against which build.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-08-28 · Cash flow — Your income, all of it (mock income-v5, 5a and 5b)</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Standard — an `audit` folder and type ||| the rulings ledger being retired (moneykeel_rulings.json · G40) — originally: the design Changelog, 2026-09-01 (approved by JJ) — swept into this ledger 2026-09-28</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1591,29 +1589,29 @@
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DEC-0205</t>
+          <t>DEC-0211</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Every statutory constant checked against its published source — three errors found</t>
+          <t>Plan hub · Retirement cockpit</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Every figure set by law is typed in from the published source. The first run against the real figures found three errors: the IRA limits were a year out of date, the bigger catch-up allowance for ages 60 to 63 was missing entirely in an app built for ages 55 to 70, and four of the required-withdrawal divisors were slightly wrong from being interpolated rather than typed.</t>
+          <t>The screens said the plan was tested against about 400 possible futures. It had been 1,000 since an earlier fix, and the screens were never updated. The number on screen must be the number the calculation actually ran.</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three </t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-02 · Plan hub · Retirement cockpit ||| the rulings ledger being retired (moneykeel_rulings.json · G44) — originally: the design Changelog, 2026-09-02 (approved by JJ) — swept into this ledger 2026-09-28</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1622,32 +1620,32 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DEC-0206</t>
+          <t>DEC-0212</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Standard — an `audit` folder and type</t>
+          <t>App-wide</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Records of checking the work get their own folder. His ruling: checking the work is its own kind of paper. Filing a device-test sheet under the standards folder hid the record of what had been verified against which build.</t>
+          <t>The wider sweep found more stragglers under the same rule and added five new patterns to the test, so the same synonyms cannot come back.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Standard — an `audit` folder and type ||| the rulings ledger being retired (moneykeel_rulings.json · G40) — originally: the design Changelog, 2026-09-01 (approved by JJ) — swept into this ledger 2026-09-28</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-02 · App-wide</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1656,32 +1654,32 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DEC-0211</t>
+          <t>DEC-0218</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Plan hub · Retirement cockpit</t>
+          <t>App-wide · top bar</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>The screens said the plan was tested against about 400 possible futures. It had been 1,000 since an earlier fix, and the screens were never updated. The number on screen must be the number the calculation actually ran.</t>
+          <t>The app name sits at the top of EVERY screen, not only the main tabs. Drawn in a mock for approval before being built.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-02 · Plan hub · Retirement cockpit ||| the rulings ledger being retired (moneykeel_rulings.json · G44) — originally: the design Changelog, 2026-09-02 (approved by JJ) — swept into this ledger 2026-09-28</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-14 · App-wide · top bar</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -1690,32 +1688,32 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DEC-0212</t>
+          <t>DEC-0229</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>App-wide</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>The wider sweep found more stragglers under the same rule and added five new patterns to the test, so the same synonyms cannot come back.</t>
+          <t>The Performance mock was redrawn with his four changes — among them, the period buttons moved onto ONE row using the app’s own corner radius instead of semicircle ends.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-02 · App-wide</t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-25 · Performance</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -1724,76 +1722,8 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0218</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>App-wide · top bar</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>The app name sits at the top of EVERY screen, not only the main tabs. Drawn in a mock for approval before being built.</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-14 · App-wide · top bar</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>DEC-0229</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>The Performance mock was redrawn with his four changes — among them, the period buttons moved onto ONE row using the app’s own corner radius instead of semicircle ends.</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-25 · Performance</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>The changelog row recorded what was built. Your wording was not written down anywhere.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:H34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
+++ b/MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx
@@ -1543,7 +1543,7 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three </t>
+          <t>FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three ||| FCC-core-detailed-design-v1.3-2026-08-14.xlsx · Changelog · 2026-09-01 · Every statutory constant checked against its published source — three</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
